--- a/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:13:46-03:00</t>
+    <t>2026-09-15T10:16:15-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T10:16:15-03:00</t>
+    <t>2026-09-21T17:12:23-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/CodeSystem-CodigoPrestacionFonasa.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T17:12:23-03:00</t>
+    <t>2026-09-22T09:29:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
